--- a/input/industry/Specific_Consumption.xlsx
+++ b/input/industry/Specific_Consumption.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{535FA81C-18CF-4E34-8BDF-DFB9204B024A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DCE3189-6354-4E3C-9119-A885BCC9FDF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30915" yWindow="1275" windowWidth="21885" windowHeight="14730" firstSheet="16" activeTab="22" xr2:uid="{2F4E5CD1-8644-4C39-AFB8-65F19E3A2B23}"/>
+    <workbookView xWindow="30315" yWindow="1485" windowWidth="20175" windowHeight="13230" firstSheet="4" activeTab="4" xr2:uid="{2F4E5CD1-8644-4C39-AFB8-65F19E3A2B23}"/>
   </bookViews>
   <sheets>
     <sheet name="steel" sheetId="9" r:id="rId1"/>
@@ -28,9 +28,11 @@
     <sheet name="ethylene_classic" sheetId="44" r:id="rId18"/>
     <sheet name="propylene" sheetId="15" r:id="rId19"/>
     <sheet name="propylene_classic" sheetId="42" r:id="rId20"/>
-    <sheet name="aromatics" sheetId="16" r:id="rId21"/>
-    <sheet name="aromatics_classic" sheetId="43" r:id="rId22"/>
-    <sheet name="Info" sheetId="2" r:id="rId23"/>
+    <sheet name="olefins" sheetId="48" r:id="rId21"/>
+    <sheet name="olefins_classic" sheetId="49" r:id="rId22"/>
+    <sheet name="aromatics" sheetId="16" r:id="rId23"/>
+    <sheet name="aromatics_classic" sheetId="43" r:id="rId24"/>
+    <sheet name="Info" sheetId="2" r:id="rId25"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="228">
   <si>
     <t>Country</t>
   </si>
@@ -303,10 +305,6 @@
   </si>
   <si>
     <t>https://www.bmwk.de/Redaktion/DE/Downloads/E/energiewende-in-der-industrie-ap2a-branchensteckbrief-metall.pdf?__blob=publicationFile&amp;v=4</t>
-  </si>
-  <si>
-    <t>elec: 14,5 MWh/t = 52,2 GJ/t
-fuel: 4,78 MWh/t * 19% = 3.27 GJ/t (81% fuel demand for the anode)</t>
   </si>
   <si>
     <t>Fuel: Further processing and anode production
@@ -342,10 +340,6 @@
   </si>
   <si>
     <t>alu_sec</t>
-  </si>
-  <si>
-    <t>elec: 0,5 MWh/t = 1.8 GJ/t
-fuel: 2,5 MWh/t = 9 GJ/t</t>
   </si>
   <si>
     <t>Fuel for smelting and total energy demand</t>
@@ -769,6 +763,20 @@
   </si>
   <si>
     <t>Assumption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">elec: 14,5 MWh/t = 52,2 GJ/t
+fuel: 4,78 MWh/t * 19% = 3.27 GJ/t (81% fuel demand for the anode)
+Casting (Gießen)
+elec: 1,6 MWh/t = 5,76 GJ/t
+fuel: 2,0 MWh/t = 7,2 GJ/t </t>
+  </si>
+  <si>
+    <t xml:space="preserve">elec: 0,5 MWh/t = 1.8 GJ/t
+fuel: 2,5 MWh/t = 9 GJ/t
+Casting (Gießen)
+elec: 1,6 MWh/t = 5,76 GJ/t
+fuel: 2,0 MWh/t = 7,2 GJ/t </t>
   </si>
 </sst>
 </file>
@@ -1261,7 +1269,7 @@
         <v>21</v>
       </c>
       <c r="G1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1286,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2203,6 +2211,111 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75F2C2B5-9BF1-47BB-9C63-AF6F88DA187A}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <f>C2+D2+F2</f>
+        <v>77.861544439999989</v>
+      </c>
+      <c r="C2">
+        <f>2.28*methanol!C2+5</f>
+        <v>17.311999999999998</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <f>2.67*methanol!F2</f>
+        <v>60.549544439999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DBCE72B-56CB-4966-8FEB-309E2772ACCD}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <f>C2+D2+F2</f>
+        <v>16.5</v>
+      </c>
+      <c r="C2">
+        <v>0.8</v>
+      </c>
+      <c r="D2">
+        <f>16.5-C2</f>
+        <v>15.7</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2255,7 +2368,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BCF0768-264A-48C8-A47A-CA806FD42378}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2308,7 +2421,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:K132"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2321,31 +2434,31 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E1" t="s">
         <v>184</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>185</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>186</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I1" t="s">
         <v>187</v>
       </c>
-      <c r="G1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>190</v>
       </c>
-      <c r="I1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J1" t="s">
-        <v>192</v>
-      </c>
       <c r="K1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -2374,19 +2487,19 @@
         <v>40</v>
       </c>
       <c r="F3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I3">
         <v>2020</v>
       </c>
       <c r="J3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -2414,7 +2527,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -2443,19 +2556,19 @@
         <v>40</v>
       </c>
       <c r="F10" t="s">
+        <v>192</v>
+      </c>
+      <c r="G10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H10" t="s">
         <v>194</v>
-      </c>
-      <c r="G10" t="s">
-        <v>191</v>
-      </c>
-      <c r="H10" t="s">
-        <v>196</v>
       </c>
       <c r="I10">
         <v>2020</v>
       </c>
       <c r="J10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -2572,19 +2685,19 @@
         <v>40</v>
       </c>
       <c r="F20" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G20" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H20" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I20">
         <v>2020</v>
       </c>
       <c r="J20" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -2607,13 +2720,13 @@
         <v>72</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F23" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>71</v>
@@ -2622,10 +2735,10 @@
         <v>2017</v>
       </c>
       <c r="J23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -2668,7 +2781,7 @@
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
     </row>
-    <row r="29" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -2679,22 +2792,22 @@
         <v>81</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>83</v>
+        <v>226</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F29" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G29" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I29">
         <v>2020</v>
       </c>
       <c r="J29" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -2710,7 +2823,7 @@
         <v>41</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="3"/>
@@ -2726,10 +2839,10 @@
         <v>47</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>1</v>
@@ -2740,28 +2853,28 @@
         <v>48</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E34" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H34" t="s">
         <v>86</v>
-      </c>
-      <c r="H34" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
     </row>
-    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -2772,22 +2885,22 @@
         <v>81</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>94</v>
+        <v>227</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F37" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G37" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I37">
         <v>2020</v>
       </c>
       <c r="J37" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -2798,10 +2911,10 @@
         <v>47</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>1</v>
@@ -2812,13 +2925,13 @@
         <v>48</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -2828,7 +2941,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B42" s="9"/>
       <c r="C42" s="11"/>
@@ -2843,33 +2956,33 @@
         <v>39</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F43" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G43" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I43">
         <v>2020</v>
       </c>
       <c r="J43" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="C44" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E44" s="3"/>
     </row>
@@ -2886,10 +2999,10 @@
         <v>47</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>1</v>
@@ -2900,16 +3013,16 @@
         <v>48</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H47" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -2919,7 +3032,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9"/>
       <c r="C49" s="11"/>
@@ -2934,33 +3047,33 @@
         <v>39</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F50" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G50" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I50">
         <v>2020</v>
       </c>
       <c r="J50" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="C51" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E51" s="3"/>
     </row>
@@ -2977,10 +3090,10 @@
         <v>47</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>1</v>
@@ -2991,16 +3104,16 @@
         <v>48</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H54" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -3010,7 +3123,7 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B56" s="9"/>
       <c r="C56" s="11"/>
@@ -3025,28 +3138,28 @@
         <v>39</v>
       </c>
       <c r="C57" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G57" t="s">
+        <v>202</v>
+      </c>
+      <c r="H57" t="s">
         <v>204</v>
-      </c>
-      <c r="H57" t="s">
-        <v>206</v>
       </c>
       <c r="I57">
         <v>2014</v>
       </c>
       <c r="J57" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K57" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -3056,48 +3169,48 @@
     </row>
     <row r="59" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B59" t="s">
         <v>41</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F59" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G59" s="21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H59" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I59">
         <v>2014</v>
       </c>
       <c r="J59" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K59" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
+        <v>116</v>
+      </c>
+      <c r="C60" t="s">
         <v>118</v>
-      </c>
-      <c r="C60" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B62" s="12"/>
       <c r="C62" s="9"/>
@@ -3112,54 +3225,54 @@
         <v>39</v>
       </c>
       <c r="C63" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F63" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G63" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I63">
         <v>2020</v>
       </c>
       <c r="J63" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B64" s="14" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C64" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E64" t="s">
         <v>1</v>
       </c>
       <c r="F64" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G64" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H64" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I64">
         <v>2014</v>
       </c>
       <c r="J64" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K64" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -3167,24 +3280,24 @@
     </row>
     <row r="66" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>41</v>
       </c>
       <c r="C66" t="s">
+        <v>127</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B67" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C67" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -3192,7 +3305,7 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B69" s="17"/>
       <c r="C69" s="9"/>
@@ -3207,36 +3320,36 @@
         <v>39</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F70" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G70" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I70">
         <v>2011</v>
       </c>
       <c r="K70" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B71" s="14" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C71" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D71" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -3244,16 +3357,16 @@
     </row>
     <row r="73" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>134</v>
+      </c>
+      <c r="B73" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B73" s="14" t="s">
+      <c r="D73" t="s">
         <v>137</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D73" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -3261,7 +3374,7 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B75" s="17"/>
       <c r="C75" s="9"/>
@@ -3276,25 +3389,25 @@
         <v>39</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F76" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G76" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H76" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I76">
         <v>2020</v>
       </c>
       <c r="J76" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -3308,7 +3421,7 @@
         <v>41</v>
       </c>
       <c r="C78" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -3316,21 +3429,21 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B80" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -3344,13 +3457,13 @@
         <v>47</v>
       </c>
       <c r="C83" s="18" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E83" t="s">
         <v>1</v>
       </c>
       <c r="H83" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -3358,7 +3471,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B85" s="9"/>
       <c r="C85" s="19"/>
@@ -3373,28 +3486,28 @@
         <v>39</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F86" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G86" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H86" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I86">
         <v>2017</v>
       </c>
       <c r="J86" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K86" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -3402,7 +3515,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B88" s="9"/>
       <c r="C88" s="19"/>
@@ -3417,25 +3530,25 @@
         <v>39</v>
       </c>
       <c r="C89" s="18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F89" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G89" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I89">
         <v>2017</v>
       </c>
       <c r="J89" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K89" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -3443,21 +3556,21 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B91" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C91" s="18" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C92" s="18" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -3465,7 +3578,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B94" s="9"/>
       <c r="C94" s="19"/>
@@ -3480,28 +3593,28 @@
         <v>39</v>
       </c>
       <c r="C95" s="18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F95" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G95" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H95" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I95">
         <v>2017</v>
       </c>
       <c r="J95" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K95" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -3524,28 +3637,28 @@
         <v>39</v>
       </c>
       <c r="C98" s="18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D98" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F98" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G98" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I98">
         <v>2017</v>
       </c>
       <c r="J98" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K98" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -3553,13 +3666,13 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B100" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C100" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -3570,7 +3683,7 @@
         <v>47</v>
       </c>
       <c r="C102" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>33</v>
@@ -3581,10 +3694,10 @@
         <v>48</v>
       </c>
       <c r="C103" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -3592,7 +3705,7 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="9" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B105" s="9"/>
       <c r="C105" s="9"/>
@@ -3607,28 +3720,28 @@
         <v>39</v>
       </c>
       <c r="C106" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D106" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F106" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G106" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I106">
         <v>2017</v>
       </c>
       <c r="J106" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K106" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
@@ -3642,10 +3755,10 @@
         <v>41</v>
       </c>
       <c r="C108" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D108" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E108" s="3"/>
     </row>
@@ -3660,10 +3773,10 @@
         <v>47</v>
       </c>
       <c r="C110" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D110" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>1</v>
@@ -3674,13 +3787,13 @@
         <v>48</v>
       </c>
       <c r="C111" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -3688,7 +3801,7 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B113" s="9"/>
       <c r="C113" s="9"/>
@@ -3703,28 +3816,28 @@
         <v>39</v>
       </c>
       <c r="C114" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D114" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F114" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G114" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I114">
         <v>2017</v>
       </c>
       <c r="J114" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K114" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -3738,10 +3851,10 @@
         <v>41</v>
       </c>
       <c r="C116" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D116" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E116" s="3"/>
     </row>
@@ -3756,7 +3869,7 @@
         <v>47</v>
       </c>
       <c r="C118" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E118" s="3"/>
     </row>
@@ -3765,7 +3878,7 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B120" s="9"/>
       <c r="C120" s="9"/>
@@ -3780,10 +3893,10 @@
         <v>39</v>
       </c>
       <c r="C121" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D121" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>33</v>
@@ -3800,13 +3913,13 @@
         <v>47</v>
       </c>
       <c r="C123" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="D123" t="s">
         <v>174</v>
       </c>
-      <c r="D123" t="s">
-        <v>176</v>
-      </c>
       <c r="E123" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="120" x14ac:dyDescent="0.25">
@@ -3814,33 +3927,33 @@
         <v>48</v>
       </c>
       <c r="C124" t="s">
+        <v>173</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F124" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G124" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I124">
         <v>2017</v>
       </c>
       <c r="J124" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K124" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B126" s="9"/>
       <c r="C126" s="9"/>
@@ -3855,28 +3968,28 @@
         <v>39</v>
       </c>
       <c r="D127" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F127" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G127" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H127" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I127">
         <v>2017</v>
       </c>
       <c r="J127" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K127" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="129" spans="2:2" x14ac:dyDescent="0.25">
@@ -4069,7 +4182,7 @@
         <v>21</v>
       </c>
       <c r="H1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -4078,13 +4191,15 @@
       </c>
       <c r="B2">
         <f>C2+D2</f>
-        <v>55.470000000000006</v>
+        <v>68.430000000000007</v>
       </c>
       <c r="C2">
-        <v>52.2</v>
+        <f>52.2+5.76</f>
+        <v>57.96</v>
       </c>
       <c r="D2">
-        <v>3.27</v>
+        <f>3.27+7.2</f>
+        <v>10.47</v>
       </c>
       <c r="E2" s="5">
         <v>20</v>
@@ -4093,7 +4208,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -4130,7 +4245,7 @@
         <v>21</v>
       </c>
       <c r="H1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -4139,13 +4254,15 @@
       </c>
       <c r="B2">
         <f>C2+D2</f>
-        <v>10.8</v>
+        <v>23.759999999999998</v>
       </c>
       <c r="C2">
-        <v>1.8</v>
+        <f>1.8+5.76</f>
+        <v>7.56</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <f>9+7.2</f>
+        <v>16.2</v>
       </c>
       <c r="E2" s="5">
         <v>20</v>
@@ -4154,7 +4271,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -4188,7 +4305,7 @@
         <v>21</v>
       </c>
       <c r="H1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -4214,7 +4331,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -4254,7 +4371,7 @@
         <v>21</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -4277,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -4770,7 +4887,7 @@
         <v>21</v>
       </c>
       <c r="H1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -4796,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
